--- a/rehearsals/blind-02/out-after-fixes/a1/a1.xlsx
+++ b/rehearsals/blind-02/out-after-fixes/a1/a1.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1375,10 +1375,14 @@
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>none stated in the documents</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
+          <t>document refused (the Proposal's fate is not stated: VOL-I 11.1(i) gate): "A Bid Bond issued by a branch of a foreign bank, whether or not confirmed, will not be accepted."</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03 Q15 p2</t>
+        </is>
+      </c>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr">
         <is>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>lesser consequence: "A Technical Proposal that does not include the report will be awarded no marks under criterion A of Table 1-1 (revised)."</t>
+          <t>zero marks under one criterion (scored; not a disqualification): "A Technical Proposal that does not include the report will be awarded no marks under criterion A of Table 1-1 (revised)."</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
@@ -5412,27 +5416,29 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.</t>
+          <t>[VOL-IV cover/T1/4-G+ADD-03 p2] (not in the volumes as issued)
+[ADD-03 7.2 p2; issued by ADD-03] (not in the volumes as issued)</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.</t>
+          <t>[VOL-IV cover/T1/4-G+ADD-03 p2] Form: 4-G | Title: Cybersecurity Compliance Undertaking | Envelope: A | Status: Mandatory
+[ADD-03 7.2 p2] The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’</t>
+          <t>Form: 4-G | Title: Cybersecurity Compliance Undertaking | Envelope: A | Status: Mandatory</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>ADD-03 7.2 p2</t>
+          <t>ADD-03 7.2 p2 (amending VOL-IV cover/T1/4-G+ADD-03)</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>ADD-03 7.2 p2</t>
+          <t>VOL-IV cover/T1/4-G+ADD-03 p2 &lt;- ADD-03/7.2; ADD-03 7.2 p2</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -5480,7 +5486,7 @@
       <c r="T38" s="4" t="inlineStr"/>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>ADD-03 7.2 p2</t>
+          <t>ADD-03 7.2 p2 (amending VOL-IV cover/T1/4-G+ADD-03)</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr">
@@ -5492,7 +5498,7 @@
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>high: verbatim; the entry is not shown as a row of the index table</t>
+          <t>high: verbatim; the entry is a row of the index table from ADD-03 [Session 09 fix, after the key: was 'verbatim; the entry is not shown as a row of the index table']</t>
         </is>
       </c>
       <c r="Z38" s="4" t="inlineStr">
@@ -5507,12 +5513,12 @@
       </c>
       <c r="AB38" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>ADD-03/7.2: proposed</t>
         </is>
       </c>
       <c r="AC38" s="4" t="inlineStr">
         <is>
-          <t>ADD-03:7.2 (ADD-03 p2; text layer; issued by ADD-03)</t>
+          <t>VOL-IV:cover/T1/4-G+ADD-03 (VOL-IV p2; addendum op; issued by ADD-03); ADD-03:7.2 (ADD-03 p2; text layer; issued by ADD-03); ADD-03/7.2 [ADD-03; proposed] &lt;- ADD-03:7.2 (ADD-03 p2)</t>
         </is>
       </c>
       <c r="AD38" s="4" t="inlineStr"/>
@@ -5881,10 +5887,14 @@
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
-          <t>none stated in the documents</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="inlineStr"/>
+          <t>document refused (the Proposal's fate is not stated: VOL-I 11.1(i) gate): "A Power of Attorney that does not comply will be treated as not submitted."</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03 Q16 p2</t>
+        </is>
+      </c>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr">
         <is>
@@ -10367,10 +10377,14 @@
       </c>
       <c r="V72" s="4" t="inlineStr">
         <is>
-          <t>none stated in the documents</t>
-        </is>
-      </c>
-      <c r="W72" s="4" t="inlineStr"/>
+          <t>document refused (the Proposal's fate is not stated: VOL-I 11.1(i) gate): "A Power of Attorney that does not comply will be treated as not submitted."</t>
+        </is>
+      </c>
+      <c r="W72" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03 Q16 p2</t>
+        </is>
+      </c>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="4" t="inlineStr">
         <is>
@@ -11457,22 +11471,22 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>The Financial Model shall be submitted in unlocked, fully formula-linked Microsoft Excel format, without macros and without hard-coded values in calculation cells.</t>
+          <t>The Financial Model shall be submitted in unlocked, fully formula-linked Microsoft Excel format, without macros and without hard-coded values in calculation cells, and shall be accompanied by an opinion from an independent model auditor addressed to the Authority.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>The Financial Model shall be submitted</t>
+          <t>shall be accompanied by an opinion from an independent model auditor addressed to the Authority</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 10.3 p5 as amended by ADD-03 4.1 p1</t>
+          <t>VOL-I 10.3 p5</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 10.3 p5 &lt;- ADD-03/4.1</t>
+          <t>VOL-I 10.3 p5</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -11510,9 +11524,9 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="Q80" s="5" t="inlineStr">
-        <is>
-          <t>AMENDED (ADD-03/4.1)</t>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED (ADD-03/4.1)</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr">
@@ -38019,7 +38033,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/7.2: the entry is given in prose, so it is recorded as an annotation, not as a new row of the index table; the cover line 'Forms 4-A to 4-F' is not amended</t>
+          <t>ADD-03/7.2: the cover line 'Forms 4-A to 4-F' (VOL-IV:cover/para4) is not amended [Session 09 fix, after the key: the first half of the scored issue (the entry recorded only as an annotation) no longer applies]</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -38163,7 +38177,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(a) ends the effect of ADD-01:Q3: 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(b) adds an obligation (VOL-I:6.4): 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q16 adds an obligation (VOL-I:9.1): 'Yes. A Power of Attorney executed outside the Kingdom shall, in addition to notarisation, be legalised by an embassy or consulate of the Kingdom in the country of execution, or apostilled where that country is a party to the Apostille Conv…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q20 adds an obligation (VOL-I:6.5, VOL-I:10.1): 'The Financial Model shall be submitted on a second, separate encrypted USB media placed in Envelope B. The electronic copy required by Volume I Clause 6.5 shall contain Envelope A only. The password for each USB media shall be submitted th…'; [omitted] ADD-03/2.2 amends ADD-01:2.1; the summary does not mention it: 'The second sentence of Section 2.1 of Addendum No. 1 (‘The time of 14:00 Riyadh time is unchanged.’) ceases to have effect.'; [omitted] ADD-03/3.1 amends VOL-I:7.1; the summary does not mention it: 'In Volume I Clause 7.1, ‘one hundred and fifty (150) days’ is deleted and ‘one hundred and eighty (180) days’ is substituted.'; [omitted] ADD-03/4.1 amends VOL-I:10.3; the summary does not mention it: 'In Volume I Clause 10.3, the words ‘, and shall be accompanied by an opinion from an independent model auditor addressed to the Authority’ are deleted. No model audit opinion is required with the Proposal.'; [omitted] ADD-03/4.2 inserts new text after VOL-I:12.4; the summary does not mention it: 'The following new Clause 12.5 is inserted in Volume I after Clause 12.4: ‘12.5 The Preferred Bidder shall deliver to the Authority, not later than forty-five (45) days after the Preferred Bidder Notification, an opinion from an independent…'; [omitted] ADD-03/5.2(a) ends the effect of ADD-02:4.1; the summary does not mention it: 'Section 4.1 of Addendum No. 2 is revoked. The period in Volume II Clause 4.4 is seventy-two (72) hours, as originally issued.'; [omitted] ADD-03/6.2 adds an obligation (ADD-03:6.2); the summary does not mention it: 'Bidders shall reflect Table 2-2 (revised) in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/7.1 renumbers VOL-I:9.1(e)+ADD-02, VOL-I:9.1(f), VOL-I:9.1(g), VOL-I:9.1(h), VOL-I:9.1(i); the summary does not mention it: 'Following the insertion of Form 4-G by Section 7.1 of Addendum No. 2, the items of Volume I Clause 9.1 are re-lettered: Form 4-G is item (f), and former items (f) to (i) become items (g) to (j) respectively. The numbered dividers in Envelo…'; [omitted] ADD-03/7.2 adds an obligation (ADD-03:7.2); the summary does not mention it: 'The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.'; [omitted] ADD-03/T2-2-rev/note(4) amends VOL-II:2.3; the summary does not mention it: '(4) In Volume II Clause 2.3, ‘50% of nominal capacity’ is deleted and ‘25% of nominal capacity’ is substituted.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(a) ends the effect of ADD-01:Q3: 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(b) adds an obligation (VOL-I:6.4): 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q16 adds an obligation (VOL-I:9.1): 'Yes. A Power of Attorney executed outside the Kingdom shall, in addition to notarisation, be legalised by an embassy or consulate of the Kingdom in the country of execution, or apostilled where that country is a party to the Apostille Conv…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q20 adds an obligation (VOL-I:6.5, VOL-I:10.1): 'The Financial Model shall be submitted on a second, separate encrypted USB media placed in Envelope B. The electronic copy required by Volume I Clause 6.5 shall contain Envelope A only. The password for each USB media shall be submitted th…'; [omitted] ADD-03/2.2 deletes words from ADD-01:2.1; the summary does not mention it: 'The second sentence of Section 2.1 of Addendum No. 1 (‘The time of 14:00 Riyadh time is unchanged.’) ceases to have effect.'; [omitted] ADD-03/3.2 amends VOL-I:6.3; the summary does not mention it: 'In Volume I Clause 6.3, ‘one hundred and eighty (180) days’ is deleted and ‘two hundred and ten (210) days’ is substituted.'; [omitted] ADD-03/4.2 inserts new text after VOL-I:12.4; the summary does not mention it: 'The following new Clause 12.5 is inserted in Volume I after Clause 12.4: ‘12.5 The Preferred Bidder shall deliver to the Authority, not later than forty-five (45) days after the Preferred Bidder Notification, an opinion from an independent…'; [omitted] ADD-03/4.3(a) deletes VOL-IV:F4-F/model-auditor; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/4.3(b) deletes VOL-IV:F4-F/date-of-model-audit-opinion; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/5.2(a) ends the effect of ADD-02:4.1; the summary does not mention it: 'Section 4.1 of Addendum No. 2 is revoked. The period in Volume II Clause 4.4 is seventy-two (72) hours, as originally issued.'; [omitted] ADD-03/6.2 adds an obligation (ADD-03:6.2); the summary does not mention it: 'Bidders shall reflect Table 2-2 (revised) in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/7.2 adds a row to VOL-IV:cover/T1 after VOL-IV:cover/T1/4-F; the summary does not mention it: 'The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.'; [omitted] ADD-03/T2-2-rev/note(4) amends VOL-II:2.3; the summary does not mention it: '(4) In Volume II Clause 2.3, ‘50% of nominal capacity’ is deleted and ‘25% of nominal capacity’ is substituted.'; [contradicted] 'The Proposal Due Date is unchanged', but ADD-03/2.1 replaces '14:00 hours Riyadh time' with '11:00 hours Riyadh time' in VOL-I 6.1; VOL-I 2.6: 'Proposal Due Date means the date and time stated in Clause 6.1, as the same may be amended by Addendum.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -38715,7 +38729,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-opinion: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01, VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
+          <t>A5 model-audit-opinion: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -38730,7 +38744,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01; VOL-I-10.3-02</t>
+          <t>ADD-03-12.5-01</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -38743,7 +38757,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-review: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01, VOL-I-10.3-02; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
+          <t>A5 model-audit-review: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -38758,7 +38772,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01; VOL-I-10.3-02</t>
+          <t>ADD-03-12.5-01</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -38771,7 +38785,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>A5 model-auditor-appoint: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01, VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
+          <t>A5 model-auditor-appoint: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -38786,7 +38800,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01; VOL-I-10.3-02</t>
+          <t>ADD-03-12.5-01</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -39066,7 +39080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -40056,7 +40070,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before 14:00 on the PDD; not stated</t>
+          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before the Proposal Due Date time stated in VOL-I 6.1 as amended (the time is derived, not assumed); not stated</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -40530,17 +40544,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>planning.delivery_cutoff_time</t>
+          <t>calendar.holidays</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>configurable planning choice</t>
+          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -40549,30 +40563,8 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>calendar.holidays</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Bid manager</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D68"/>
+  <autoFilter ref="A1:D67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/rehearsals/blind-02/out-after-fixes/a1/a1.xlsx
+++ b/rehearsals/blind-02/out-after-fixes/a1/a1.xlsx
@@ -13,14 +13,16 @@
     <sheet name="Stages" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Date coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Relationships" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AD$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AE$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Relationships'!$A$1:$O$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD217"/>
+  <dimension ref="A1:AE217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -511,6 +513,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="50" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,6 +681,11 @@
           <t>Issues</t>
         </is>
       </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Relationships (curated links, their status; reached at the validated stage; documents not supplied)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -826,6 +834,7 @@
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -974,6 +983,7 @@
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1122,6 +1132,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1266,6 +1277,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1414,6 +1426,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1562,6 +1575,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1710,6 +1724,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1860,6 +1875,7 @@
         </is>
       </c>
       <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2010,6 +2026,7 @@
           <t>I-LCC-ISSUER</t>
         </is>
       </c>
+      <c r="AE13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2162,6 +2179,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2302,6 +2320,7 @@
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2450,6 +2469,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2594,6 +2614,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2744,6 +2765,11 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2892,6 +2918,7 @@
           <t>I-READING-F4C; I-F4C-EXCLUSION</t>
         </is>
       </c>
+      <c r="AE19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3038,6 +3065,11 @@
       <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>I-READING-F4C</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -3182,6 +3214,7 @@
           <t>I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AE21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3318,6 +3351,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3454,6 +3488,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3590,6 +3625,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3726,6 +3762,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3866,6 +3903,7 @@
         </is>
       </c>
       <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4006,6 +4044,7 @@
         </is>
       </c>
       <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AE27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4146,6 +4185,7 @@
         </is>
       </c>
       <c r="AD28" s="4" t="inlineStr"/>
+      <c r="AE28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4286,6 +4326,7 @@
         </is>
       </c>
       <c r="AD29" s="4" t="inlineStr"/>
+      <c r="AE29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4430,6 +4471,7 @@
         </is>
       </c>
       <c r="AD30" s="4" t="inlineStr"/>
+      <c r="AE30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4570,6 +4612,7 @@
         </is>
       </c>
       <c r="AD31" s="4" t="inlineStr"/>
+      <c r="AE31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4710,6 +4753,7 @@
         </is>
       </c>
       <c r="AD32" s="4" t="inlineStr"/>
+      <c r="AE32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4852,6 +4896,11 @@
       <c r="AD33" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AE33" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -4992,6 +5041,7 @@
         </is>
       </c>
       <c r="AD34" s="4" t="inlineStr"/>
+      <c r="AE34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -5126,6 +5176,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5256,6 +5307,7 @@
         </is>
       </c>
       <c r="AD36" s="4" t="inlineStr"/>
+      <c r="AE36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5392,6 +5444,7 @@
           <t>I-ADD03-NOTE4</t>
         </is>
       </c>
+      <c r="AE37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5522,6 +5575,7 @@
         </is>
       </c>
       <c r="AD38" s="4" t="inlineStr"/>
+      <c r="AE38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5658,6 +5712,7 @@
           <t>I-ADD03-Q20</t>
         </is>
       </c>
+      <c r="AE39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5790,6 +5845,7 @@
           <t>I-ADD03-Q20; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5926,6 +5982,7 @@
           <t>I-ADD03-Q16</t>
         </is>
       </c>
+      <c r="AE41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -6074,6 +6131,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6214,6 +6272,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6352,6 +6411,7 @@
           <t>I-NO-CONSEQUENCE; I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -6490,6 +6550,7 @@
           <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
+      <c r="AE45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -6626,6 +6687,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6762,6 +6824,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6898,6 +6961,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -7046,6 +7110,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -7194,6 +7259,7 @@
           <t>I-VOL-I-ENV-B; I-VOL-I-ENV-A-PRICES; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -7346,6 +7412,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7486,6 +7553,7 @@
         </is>
       </c>
       <c r="AD52" s="4" t="inlineStr"/>
+      <c r="AE52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -7634,6 +7702,7 @@
         </is>
       </c>
       <c r="AD53" s="4" t="inlineStr"/>
+      <c r="AE53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -7778,6 +7847,7 @@
         </is>
       </c>
       <c r="AD54" s="4" t="inlineStr"/>
+      <c r="AE54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7918,6 +7988,7 @@
         </is>
       </c>
       <c r="AD55" s="4" t="inlineStr"/>
+      <c r="AE55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -8062,6 +8133,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -8206,6 +8278,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -8354,6 +8427,7 @@
           <t>I-VOL-I-ENV-A-PRICES</t>
         </is>
       </c>
+      <c r="AE58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -8498,6 +8572,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-COPIES</t>
         </is>
       </c>
+      <c r="AE59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8648,6 +8723,7 @@
           <t>I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AE60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -8796,6 +8872,7 @@
         </is>
       </c>
       <c r="AD61" s="4" t="inlineStr"/>
+      <c r="AE61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8936,6 +9013,7 @@
         </is>
       </c>
       <c r="AD62" s="4" t="inlineStr"/>
+      <c r="AE62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9084,6 +9162,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9230,6 +9309,11 @@
       <c r="AD64" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AE64" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -9376,6 +9460,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE65" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -9520,6 +9609,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE66" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -9666,6 +9760,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -9810,6 +9905,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -9958,6 +10054,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE69" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-INVESTMENT-LICENCE [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -10104,6 +10205,11 @@
       <c r="AD70" s="4" t="inlineStr">
         <is>
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AE70" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -10268,6 +10374,7 @@
           <t>I-NO-CONSEQUENCE; I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AE71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -10416,6 +10523,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -10564,6 +10672,7 @@
           <t>I-VOL-I-APPENDICES</t>
         </is>
       </c>
+      <c r="AE73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -10714,6 +10823,7 @@
           <t>I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -10864,6 +10974,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -11010,6 +11121,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -11154,6 +11266,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -11298,6 +11411,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE78" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-QUOTED-PRICE [confirmed feeds_calculation] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -11442,6 +11560,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AE79" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCIAL-MODEL [proposed depends_on] from calc:availability-payment; -&gt; REL-MODEL-FORM-4F [confirmed feeds_calculation] to VOL-IV-F4F-02</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -11586,6 +11709,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -11730,6 +11854,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11874,6 +11999,7 @@
         </is>
       </c>
       <c r="AD82" s="4" t="inlineStr"/>
+      <c r="AE82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -12018,6 +12144,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -12162,6 +12289,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE84" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCING-ASSUMPTIONS [possible depends_on] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -12306,6 +12438,7 @@
         </is>
       </c>
       <c r="AD85" s="4" t="inlineStr"/>
+      <c r="AE85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -12446,6 +12579,7 @@
         </is>
       </c>
       <c r="AD86" s="4" t="inlineStr"/>
+      <c r="AE86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -12586,6 +12720,7 @@
         </is>
       </c>
       <c r="AD87" s="4" t="inlineStr"/>
+      <c r="AE87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -12726,6 +12861,7 @@
         </is>
       </c>
       <c r="AD88" s="4" t="inlineStr"/>
+      <c r="AE88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -12866,6 +13002,7 @@
         </is>
       </c>
       <c r="AD89" s="4" t="inlineStr"/>
+      <c r="AE89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -13014,6 +13151,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -13158,6 +13296,7 @@
         </is>
       </c>
       <c r="AD91" s="4" t="inlineStr"/>
+      <c r="AE91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -13310,6 +13449,7 @@
           <t>I-VOL-I-BOND-LONGSTOP</t>
         </is>
       </c>
+      <c r="AE92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -13450,6 +13590,7 @@
         </is>
       </c>
       <c r="AD93" s="4" t="inlineStr"/>
+      <c r="AE93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -13594,6 +13735,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -13738,6 +13880,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -13878,6 +14021,7 @@
         </is>
       </c>
       <c r="AD96" s="4" t="inlineStr"/>
+      <c r="AE96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -14022,6 +14166,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -14162,6 +14307,7 @@
         </is>
       </c>
       <c r="AD98" s="4" t="inlineStr"/>
+      <c r="AE98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -14316,6 +14462,7 @@
         </is>
       </c>
       <c r="AD99" s="4" t="inlineStr"/>
+      <c r="AE99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -14456,6 +14603,7 @@
         </is>
       </c>
       <c r="AD100" s="4" t="inlineStr"/>
+      <c r="AE100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -14596,6 +14744,7 @@
         </is>
       </c>
       <c r="AD101" s="4" t="inlineStr"/>
+      <c r="AE101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -14736,6 +14885,7 @@
         </is>
       </c>
       <c r="AD102" s="4" t="inlineStr"/>
+      <c r="AE102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -14882,6 +15032,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE103" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -15030,6 +15185,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE104" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -15174,6 +15334,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE105" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -15318,6 +15483,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE106" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -15462,6 +15632,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE107" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -15606,6 +15781,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE108" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -15750,6 +15930,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE109" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -15894,6 +16079,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE110" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -16038,6 +16228,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE111" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -16182,6 +16377,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE112" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -16326,6 +16526,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE113" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -16468,6 +16673,11 @@
       <c r="AD114" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AE114" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -16628,6 +16838,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AE115" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-PROCESS-DESIGN [confirmed limit_applies] from VOL-II:T2-4</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -16768,6 +16983,7 @@
         </is>
       </c>
       <c r="AD116" s="4" t="inlineStr"/>
+      <c r="AE116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -16908,6 +17124,7 @@
         </is>
       </c>
       <c r="AD117" s="4" t="inlineStr"/>
+      <c r="AE117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -17052,6 +17269,7 @@
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -17192,6 +17410,7 @@
         </is>
       </c>
       <c r="AD119" s="4" t="inlineStr"/>
+      <c r="AE119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -17332,6 +17551,7 @@
         </is>
       </c>
       <c r="AD120" s="4" t="inlineStr"/>
+      <c r="AE120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -17476,6 +17696,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -17620,6 +17841,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -17764,6 +17986,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -17904,6 +18127,7 @@
         </is>
       </c>
       <c r="AD124" s="4" t="inlineStr"/>
+      <c r="AE124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -18048,6 +18272,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -18188,6 +18413,7 @@
         </is>
       </c>
       <c r="AD126" s="4" t="inlineStr"/>
+      <c r="AE126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -18328,6 +18554,7 @@
         </is>
       </c>
       <c r="AD127" s="4" t="inlineStr"/>
+      <c r="AE127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -18472,6 +18699,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -18612,6 +18840,7 @@
         </is>
       </c>
       <c r="AD129" s="4" t="inlineStr"/>
+      <c r="AE129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -18756,6 +18985,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE130" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -18896,6 +19130,7 @@
         </is>
       </c>
       <c r="AD131" s="4" t="inlineStr"/>
+      <c r="AE131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -19036,6 +19271,7 @@
         </is>
       </c>
       <c r="AD132" s="4" t="inlineStr"/>
+      <c r="AE132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -19180,6 +19416,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -19326,6 +19563,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -19470,6 +19708,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -19610,6 +19849,7 @@
         </is>
       </c>
       <c r="AD136" s="4" t="inlineStr"/>
+      <c r="AE136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -19750,6 +19990,7 @@
         </is>
       </c>
       <c r="AD137" s="4" t="inlineStr"/>
+      <c r="AE137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -19894,6 +20135,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -20034,6 +20276,7 @@
         </is>
       </c>
       <c r="AD139" s="4" t="inlineStr"/>
+      <c r="AE139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -20174,6 +20417,7 @@
         </is>
       </c>
       <c r="AD140" s="4" t="inlineStr"/>
+      <c r="AE140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -20314,6 +20558,7 @@
         </is>
       </c>
       <c r="AD141" s="4" t="inlineStr"/>
+      <c r="AE141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -20454,6 +20699,7 @@
         </is>
       </c>
       <c r="AD142" s="4" t="inlineStr"/>
+      <c r="AE142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -20594,6 +20840,7 @@
         </is>
       </c>
       <c r="AD143" s="4" t="inlineStr"/>
+      <c r="AE143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -20734,6 +20981,7 @@
         </is>
       </c>
       <c r="AD144" s="4" t="inlineStr"/>
+      <c r="AE144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -20874,6 +21122,7 @@
         </is>
       </c>
       <c r="AD145" s="4" t="inlineStr"/>
+      <c r="AE145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -21018,6 +21267,7 @@
         </is>
       </c>
       <c r="AD146" s="4" t="inlineStr"/>
+      <c r="AE146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -21158,6 +21408,7 @@
         </is>
       </c>
       <c r="AD147" s="4" t="inlineStr"/>
+      <c r="AE147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -21298,6 +21549,7 @@
         </is>
       </c>
       <c r="AD148" s="4" t="inlineStr"/>
+      <c r="AE148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -21438,6 +21690,7 @@
         </is>
       </c>
       <c r="AD149" s="4" t="inlineStr"/>
+      <c r="AE149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -21586,6 +21839,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AE150" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RELIABILITY-RUN [confirmed limit_applies] from VOL-II:T2-4</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -21734,6 +21992,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -21874,6 +22133,7 @@
         </is>
       </c>
       <c r="AD152" s="4" t="inlineStr"/>
+      <c r="AE152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -22018,6 +22278,7 @@
         </is>
       </c>
       <c r="AD153" s="4" t="inlineStr"/>
+      <c r="AE153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -22158,6 +22419,7 @@
         </is>
       </c>
       <c r="AD154" s="4" t="inlineStr"/>
+      <c r="AE154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -22298,6 +22560,7 @@
         </is>
       </c>
       <c r="AD155" s="4" t="inlineStr"/>
+      <c r="AE155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -22438,6 +22701,7 @@
         </is>
       </c>
       <c r="AD156" s="4" t="inlineStr"/>
+      <c r="AE156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -22578,6 +22842,7 @@
         </is>
       </c>
       <c r="AD157" s="4" t="inlineStr"/>
+      <c r="AE157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -22726,6 +22991,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -22874,6 +23140,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -23018,6 +23285,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -23158,6 +23426,7 @@
         </is>
       </c>
       <c r="AD161" s="4" t="inlineStr"/>
+      <c r="AE161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -23302,6 +23571,7 @@
         </is>
       </c>
       <c r="AD162" s="4" t="inlineStr"/>
+      <c r="AE162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -23446,6 +23716,7 @@
         </is>
       </c>
       <c r="AD163" s="4" t="inlineStr"/>
+      <c r="AE163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -23586,6 +23857,7 @@
         </is>
       </c>
       <c r="AD164" s="4" t="inlineStr"/>
+      <c r="AE164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -23726,6 +23998,7 @@
         </is>
       </c>
       <c r="AD165" s="4" t="inlineStr"/>
+      <c r="AE165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -23874,6 +24147,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -24052,6 +24326,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -24196,6 +24471,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -24344,6 +24620,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -24488,6 +24765,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -24632,6 +24910,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -24776,6 +25055,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -24950,6 +25230,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -25094,6 +25375,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -25238,6 +25520,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE175" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -25382,6 +25669,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE176" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -25526,6 +25818,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -25692,6 +25985,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -25832,6 +26126,7 @@
         </is>
       </c>
       <c r="AD179" s="4" t="inlineStr"/>
+      <c r="AE179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -25972,6 +26267,7 @@
         </is>
       </c>
       <c r="AD180" s="4" t="inlineStr"/>
+      <c r="AE180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -26112,6 +26408,7 @@
         </is>
       </c>
       <c r="AD181" s="4" t="inlineStr"/>
+      <c r="AE181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -26252,6 +26549,7 @@
         </is>
       </c>
       <c r="AD182" s="4" t="inlineStr"/>
+      <c r="AE182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -26392,6 +26690,7 @@
         </is>
       </c>
       <c r="AD183" s="4" t="inlineStr"/>
+      <c r="AE183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -26532,6 +26831,7 @@
         </is>
       </c>
       <c r="AD184" s="4" t="inlineStr"/>
+      <c r="AE184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -26672,6 +26972,7 @@
         </is>
       </c>
       <c r="AD185" s="4" t="inlineStr"/>
+      <c r="AE185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -26834,6 +27135,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -27008,6 +27310,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE187" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FORM-4F [confirmed feeds_calculation] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -27152,6 +27459,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE188" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MODEL-FORM-4F [confirmed feeds_calculation] from VOL-I-10.3-01; REACHED at ADD-03 (confirmed dependency): from VOL-I-10.3-01 via REL-MODEL-FORM-4F</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -27300,6 +27612,7 @@
           <t>I-VOL-V-MISSING; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -27448,6 +27761,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -27592,6 +27906,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -27740,6 +28055,7 @@
         </is>
       </c>
       <c r="AD192" s="4" t="inlineStr"/>
+      <c r="AE192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -27888,6 +28204,7 @@
         </is>
       </c>
       <c r="AD193" s="4" t="inlineStr"/>
+      <c r="AE193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -28028,6 +28345,7 @@
         </is>
       </c>
       <c r="AD194" s="4" t="inlineStr"/>
+      <c r="AE194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -28168,6 +28486,7 @@
         </is>
       </c>
       <c r="AD195" s="4" t="inlineStr"/>
+      <c r="AE195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -28308,6 +28627,7 @@
         </is>
       </c>
       <c r="AD196" s="4" t="inlineStr"/>
+      <c r="AE196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -28448,6 +28768,7 @@
         </is>
       </c>
       <c r="AD197" s="4" t="inlineStr"/>
+      <c r="AE197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -28588,6 +28909,7 @@
         </is>
       </c>
       <c r="AD198" s="4" t="inlineStr"/>
+      <c r="AE198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -28728,6 +29050,7 @@
         </is>
       </c>
       <c r="AD199" s="4" t="inlineStr"/>
+      <c r="AE199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -28868,6 +29191,7 @@
         </is>
       </c>
       <c r="AD200" s="4" t="inlineStr"/>
+      <c r="AE200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -29008,6 +29332,7 @@
         </is>
       </c>
       <c r="AD201" s="4" t="inlineStr"/>
+      <c r="AE201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -29166,6 +29491,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE202" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RAMP-UP-DEDUCTIONS [confirmed limit_applies] from VOL-II:T2-4</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -29310,6 +29640,7 @@
         </is>
       </c>
       <c r="AD203" s="4" t="inlineStr"/>
+      <c r="AE203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -29458,6 +29789,11 @@
           <t>I-VOL-V-MISSING; I-FLOWS</t>
         </is>
       </c>
+      <c r="AE204" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -29606,6 +29942,11 @@
           <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING</t>
         </is>
       </c>
+      <c r="AE205" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-UNAVAILABILITY [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -29752,6 +30093,11 @@
       <c r="AD206" s="4" t="inlineStr">
         <is>
           <t>I-VOL-III; I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AE206" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
         </is>
       </c>
     </row>
@@ -29894,6 +30240,7 @@
         </is>
       </c>
       <c r="AD207" s="4" t="inlineStr"/>
+      <c r="AE207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -30034,6 +30381,7 @@
         </is>
       </c>
       <c r="AD208" s="4" t="inlineStr"/>
+      <c r="AE208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -30182,6 +30530,11 @@
           <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
+      <c r="AE209" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): cannot be established: whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -30330,6 +30683,7 @@
         </is>
       </c>
       <c r="AD210" s="4" t="inlineStr"/>
+      <c r="AE210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -30470,6 +30824,7 @@
         </is>
       </c>
       <c r="AD211" s="4" t="inlineStr"/>
+      <c r="AE211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -30616,6 +30971,11 @@
       <c r="AD212" s="4" t="inlineStr">
         <is>
           <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AE212" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): cannot be established: which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
         </is>
       </c>
     </row>
@@ -30762,6 +31122,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -30902,6 +31263,7 @@
         </is>
       </c>
       <c r="AD214" s="4" t="inlineStr"/>
+      <c r="AE214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -31050,6 +31412,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -31190,6 +31553,7 @@
         </is>
       </c>
       <c r="AD216" s="4" t="inlineStr"/>
+      <c r="AE216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -31330,9 +31694,10 @@
         </is>
       </c>
       <c r="AD217" s="4" t="inlineStr"/>
+      <c r="AE217" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD217"/>
+  <autoFilter ref="A4:AE217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36802,7 +37167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -37764,94 +38129,106 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -37860,12 +38237,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -37884,12 +38261,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -37908,12 +38285,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -37932,12 +38309,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -37956,12 +38333,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/2.3</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/2.3: the reissued Form 4-A (ADD-01 App A) still prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time': both its date and now its time differ from VOL-I 6.1 as amended</t>
+          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -37980,12 +38357,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/3.3</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/3.3: ADD-03 3.3 refers to paragraph 2 of Form 4-A, which exists only in the form as originally issued; the reissued form (ADD-01 App A) has no paragraph 2 (see also I-F4A-FIELDS)</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -38004,12 +38381,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/6.1</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/6.1: the process design basis changes (nitrogen load and minimum temperature); rows citing Table 2-2 are re-read at this stage</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -38028,12 +38405,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/7.2</t>
+          <t>I-OP-ADD-03/2.3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/7.2: the cover line 'Forms 4-A to 4-F' (VOL-IV:cover/para4) is not amended [Session 09 fix, after the key: the first half of the scored issue (the entry recorded only as an annotation) no longer applies]</t>
+          <t>ADD-03/2.3: the reissued Form 4-A (ADD-01 App A) still prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time': both its date and now its time differ from VOL-I 6.1 as amended</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -38052,12 +38429,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/Q15(b)</t>
+          <t>I-OP-ADD-03/3.3</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/Q15(b): a clarification answer narrows VOL-I 6.4 ('a bank licensed to operate in the Kingdom') to a bank incorporated in the Kingdom: a substantive change made in an answer, not in the body of an Addendum</t>
+          <t>ADD-03/3.3: ADD-03 3.3 refers to paragraph 2 of Form 4-A, which exists only in the form as originally issued; the reissued form (ADD-01 App A) has no paragraph 2 (see also I-F4A-FIELDS)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -38076,12 +38453,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/Q16</t>
+          <t>I-OP-ADD-03/6.1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/Q16: the answer cites the list by its re-lettered letter: read as issued, item (i) is the Section 8 certificates, not the Powers of Attorney</t>
+          <t>ADD-03/6.1: the process design basis changes (nitrogen load and minimum temperature); rows citing Table 2-2 are re-read at this stage</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -38100,12 +38477,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/Q20</t>
+          <t>I-OP-ADD-03/7.2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/Q20: a submission rule (a second USB, passwords after the deadline) set in a clarification answer; VOL-I 6.5 still reads 'one (1) searchable electronic copy'</t>
+          <t>ADD-03/7.2: the cover line 'Forms 4-A to 4-F' (VOL-IV:cover/para4) is not amended [Session 09 fix, after the key: the first half of the scored issue (the entry recorded only as an annotation) no longer applies]</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -38124,12 +38501,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-03/Q15(b)</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/Q15(b): a clarification answer narrows VOL-I 6.4 ('a bank licensed to operate in the Kingdom') to a bank incorporated in the Kingdom: a substantive change made in an answer, not in the body of an Addendum</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -38139,7 +38516,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -38148,12 +38525,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-OP-ADD-03/Q16</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/Q16: the answer cites the list by its re-lettered letter: read as issued, item (i) is the Section 8 certificates, not the Powers of Attorney</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -38163,7 +38540,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -38172,12 +38549,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-03</t>
+          <t>I-OP-ADD-03/Q20</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(a) ends the effect of ADD-01:Q3: 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(b) adds an obligation (VOL-I:6.4): 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q16 adds an obligation (VOL-I:9.1): 'Yes. A Power of Attorney executed outside the Kingdom shall, in addition to notarisation, be legalised by an embassy or consulate of the Kingdom in the country of execution, or apostilled where that country is a party to the Apostille Conv…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q20 adds an obligation (VOL-I:6.5, VOL-I:10.1): 'The Financial Model shall be submitted on a second, separate encrypted USB media placed in Envelope B. The electronic copy required by Volume I Clause 6.5 shall contain Envelope A only. The password for each USB media shall be submitted th…'; [omitted] ADD-03/2.2 deletes words from ADD-01:2.1; the summary does not mention it: 'The second sentence of Section 2.1 of Addendum No. 1 (‘The time of 14:00 Riyadh time is unchanged.’) ceases to have effect.'; [omitted] ADD-03/3.2 amends VOL-I:6.3; the summary does not mention it: 'In Volume I Clause 6.3, ‘one hundred and eighty (180) days’ is deleted and ‘two hundred and ten (210) days’ is substituted.'; [omitted] ADD-03/4.2 inserts new text after VOL-I:12.4; the summary does not mention it: 'The following new Clause 12.5 is inserted in Volume I after Clause 12.4: ‘12.5 The Preferred Bidder shall deliver to the Authority, not later than forty-five (45) days after the Preferred Bidder Notification, an opinion from an independent…'; [omitted] ADD-03/4.3(a) deletes VOL-IV:F4-F/model-auditor; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/4.3(b) deletes VOL-IV:F4-F/date-of-model-audit-opinion; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/5.2(a) ends the effect of ADD-02:4.1; the summary does not mention it: 'Section 4.1 of Addendum No. 2 is revoked. The period in Volume II Clause 4.4 is seventy-two (72) hours, as originally issued.'; [omitted] ADD-03/6.2 adds an obligation (ADD-03:6.2); the summary does not mention it: 'Bidders shall reflect Table 2-2 (revised) in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/7.2 adds a row to VOL-IV:cover/T1 after VOL-IV:cover/T1/4-F; the summary does not mention it: 'The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.'; [omitted] ADD-03/T2-2-rev/note(4) amends VOL-II:2.3; the summary does not mention it: '(4) In Volume II Clause 2.3, ‘50% of nominal capacity’ is deleted and ‘25% of nominal capacity’ is substituted.'; [contradicted] 'The Proposal Due Date is unchanged', but ADD-03/2.1 replaces '14:00 hours Riyadh time' with '11:00 hours Riyadh time' in VOL-I 6.1; VOL-I 2.6: 'Proposal Due Date means the date and time stated in Clause 6.1, as the same may be amended by Addendum.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/Q20: a submission rule (a second USB, passwords after the deadline) set in a clarification answer; VOL-I 6.5 still reads 'one (1) searchable electronic copy'</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -38187,7 +38564,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -38196,12 +38573,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -38211,7 +38588,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -38220,101 +38597,89 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 20 WD (total float -20 WD: latest start 2026-10-06 is before the planning date 2026-11-03; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-SUMMARY-ADD-03</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-11-03; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(a) ends the effect of ADD-01:Q3: 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q15(b) adds an obligation (VOL-I:6.4): 'The response to clarification request 3 in Addendum No. 1 is withdrawn. The Bid Bond shall be issued by a bank incorporated in the Kingdom that meets the rating requirement in Volume I Clause 6.4. A Bid Bond issued by a branch of a foreign…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q16 adds an obligation (VOL-I:9.1): 'Yes. A Power of Attorney executed outside the Kingdom shall, in addition to notarisation, be legalised by an embassy or consulate of the Kingdom in the country of execution, or apostilled where that country is a party to the Apostille Conv…'; [understated] 'responds to clarification requests 15 to 21', but ADD-03/Q20 adds an obligation (VOL-I:6.5, VOL-I:10.1): 'The Financial Model shall be submitted on a second, separate encrypted USB media placed in Envelope B. The electronic copy required by Volume I Clause 6.5 shall contain Envelope A only. The password for each USB media shall be submitted th…'; [omitted] ADD-03/2.2 deletes words from ADD-01:2.1; the summary does not mention it: 'The second sentence of Section 2.1 of Addendum No. 1 (‘The time of 14:00 Riyadh time is unchanged.’) ceases to have effect.'; [omitted] ADD-03/3.2 amends VOL-I:6.3; the summary does not mention it: 'In Volume I Clause 6.3, ‘one hundred and eighty (180) days’ is deleted and ‘two hundred and ten (210) days’ is substituted.'; [omitted] ADD-03/4.2 inserts new text after VOL-I:12.4; the summary does not mention it: 'The following new Clause 12.5 is inserted in Volume I after Clause 12.4: ‘12.5 The Preferred Bidder shall deliver to the Authority, not later than forty-five (45) days after the Preferred Bidder Notification, an opinion from an independent…'; [omitted] ADD-03/4.3(a) deletes VOL-IV:F4-F/model-auditor; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/4.3(b) deletes VOL-IV:F4-F/date-of-model-audit-opinion; the summary does not mention it: 'In Form 4-F, the rows ‘Model auditor’ and ‘Date of model audit opinion’ are deleted.'; [omitted] ADD-03/5.2(a) ends the effect of ADD-02:4.1; the summary does not mention it: 'Section 4.1 of Addendum No. 2 is revoked. The period in Volume II Clause 4.4 is seventy-two (72) hours, as originally issued.'; [omitted] ADD-03/6.2 adds an obligation (ADD-03:6.2); the summary does not mention it: 'Bidders shall reflect Table 2-2 (revised) in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/7.2 adds a row to VOL-IV:cover/T1 after VOL-IV:cover/T1/4-F; the summary does not mention it: 'The Index of Forms in Volume IV is amended by adding, after the entry for Form 4-F, an entry for Form 4-G with the title ‘Cybersecurity Compliance Undertaking’, Envelope ‘A’ and Status ‘Mandatory’.'; [omitted] ADD-03/T2-2-rev/note(4) amends VOL-II:2.3; the summary does not mention it: '(4) In Volume II Clause 2.3, ‘50% of nominal capacity’ is deleted and ‘25% of nominal capacity’ is substituted.'; [contradicted] 'The Proposal Due Date is unchanged', but ADD-03/2.1 replaces '14:00 hours Riyadh time' with '11:00 hours Riyadh time' in VOL-I 6.1; VOL-I 2.6: 'Proposal Due Date means the date and time stated in Clause 6.1, as the same may be amended by Addendum.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 20 WD (total float -20 WD: latest start 2026-10-13 is before the planning date 2026-11-03; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>I-A5-pcg-wording</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>A5 pcg-wording: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_wording)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 20 WD (total float -20 WD: latest start 2026-10-06 is before the planning date 2026-11-03; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -38324,7 +38689,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
@@ -38332,17 +38697,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>I-A5-poa-resolutions</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>A5 poa-resolutions: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 5 WD is an ASSUMPTION: poa_board_resolutions)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-11-03; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -38352,7 +38717,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-Q16-01; VOL-I-9.1h-01; VOL-I-9.3-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
@@ -38360,17 +38725,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>I-A5-technical-proposal</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>A5 technical-proposal: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (ADD-02-5.2-01, ADD-02-T1-1-N3-01, ADD-03-6.2-01, ADD-03-T22n3-01, VOL-I-11.3-01, VOL-I-9.2-01, VOL-I-9.7-01, VOL-I-T1-1-A, VOL-I-T1-1-B, VOL-I-T1-1-C, VOL-I-T1-1-D, VOL-I-T1-1-E, VOL-I-T1-1-F, VOL-II-1.1-01, VOL-II-1.2-01, VOL-II-1.3-01, VOL-II-1.4-01, VOL-II-2.1-01, VOL-II-2.2-01, VOL-II-2.2-02, VOL-II-2.3-01, VOL-II-2.4-01, VOL-II-2.5-01, VOL-II-3.1-01, VOL-II-3.2-01, VOL-II-3.2-02, VOL-II-3.3-01, VOL-II-3.4-01, VOL-II-3.5-01, VOL-II-4.1-01, VOL-II-4.3-01, VOL-II-4.3-02, VOL-II-4.4-01, VOL-II-4.4-02, VOL-II-4.5-01, VOL-II-5.1-01, VOL-II-5.2-01, VOL-II-5.2-02, VOL-II-5.3-01, VOL-II-5.3-02, VOL-II-5.4-01, VOL-II-5.4-02, VOL-II-5.5-01, VOL-II-5.5-02, VOL-II-6.1-01, VOL-II-6.1-02, VOL-II-6.2-01, VOL-II-6.3-01, VOL-II-6.3-02, VOL-II-6.4-01, VOL-II-6.4-02, VOL-II-7.1-01, VOL-II-7.2-01, VOL-II-7.4-01, VOL-II-8.1-01, VOL-II-8.2-01, VOL-II-8.3-01, VOL-II-8.3-02, VOL-II-8.4-01, VOL-II-8.4-02, VOL-II-8.5-01, VOL-II-8.5-02, VOL-II-9.1-01, VOL-II-9.1-02, VOL-II-9.2-01, VOL-II-9.3-01, VOL-II-9.4-01, VOL-II-9.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-II-T2-6-1, VOL-II-T2-6-2, VOL-II-T2-6-3, VOL-II-T2-6-4, VOL-II-T2-6-5, VOL-II-T2-6-6; duration 20 WD is an ASSUMPTION: technical_proposal)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 20 WD (total float -20 WD: latest start 2026-10-13 is before the planning date 2026-11-03; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -38380,7 +38745,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-6.2-01; ADD-03-T22n3-01; VOL-I-11.3-01; VOL-I-9.2-01; VOL-I-9.7-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -38388,17 +38753,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-model-build</t>
+          <t>I-A5-pcg-wording</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-model-build: INFEASIBLE by 3 WD (total float -3 WD: latest start 2026-10-29 is before the planning date 2026-11-03; not compressed) (ADD-03-Q20-01, VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 15 WD is an ASSUMPTION: fin_model_build)</t>
+          <t>A5 pcg-wording: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_wording)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -38408,7 +38773,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-Q20-01; VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
+          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -38416,12 +38781,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>I-A5-poa</t>
+          <t>I-A5-poa-resolutions</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>A5 poa: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-10 (after poa-resolutions) is after the latest start 2026-11-03; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 5 WD is an ASSUMPTION: poa_notarisation)</t>
+          <t>A5 poa-resolutions: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 5 WD is an ASSUMPTION: poa_board_resolutions)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -38444,17 +38809,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>I-A5-pcg-execution</t>
+          <t>I-A5-technical-proposal</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>A5 pcg-execution: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-17 (after pcg-wording) is after the latest start 2026-11-10; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_execution)</t>
+          <t>A5 technical-proposal: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-27 is before the planning date 2026-11-03; not compressed) (ADD-02-5.2-01, ADD-02-T1-1-N3-01, ADD-03-6.2-01, ADD-03-T22n3-01, VOL-I-11.3-01, VOL-I-9.2-01, VOL-I-9.7-01, VOL-I-T1-1-A, VOL-I-T1-1-B, VOL-I-T1-1-C, VOL-I-T1-1-D, VOL-I-T1-1-E, VOL-I-T1-1-F, VOL-II-1.1-01, VOL-II-1.2-01, VOL-II-1.3-01, VOL-II-1.4-01, VOL-II-2.1-01, VOL-II-2.2-01, VOL-II-2.2-02, VOL-II-2.3-01, VOL-II-2.4-01, VOL-II-2.5-01, VOL-II-3.1-01, VOL-II-3.2-01, VOL-II-3.2-02, VOL-II-3.3-01, VOL-II-3.4-01, VOL-II-3.5-01, VOL-II-4.1-01, VOL-II-4.3-01, VOL-II-4.3-02, VOL-II-4.4-01, VOL-II-4.4-02, VOL-II-4.5-01, VOL-II-5.1-01, VOL-II-5.2-01, VOL-II-5.2-02, VOL-II-5.3-01, VOL-II-5.3-02, VOL-II-5.4-01, VOL-II-5.4-02, VOL-II-5.5-01, VOL-II-5.5-02, VOL-II-6.1-01, VOL-II-6.1-02, VOL-II-6.2-01, VOL-II-6.3-01, VOL-II-6.3-02, VOL-II-6.4-01, VOL-II-6.4-02, VOL-II-7.1-01, VOL-II-7.2-01, VOL-II-7.4-01, VOL-II-8.1-01, VOL-II-8.2-01, VOL-II-8.3-01, VOL-II-8.3-02, VOL-II-8.4-01, VOL-II-8.4-02, VOL-II-8.5-01, VOL-II-8.5-02, VOL-II-9.1-01, VOL-II-9.1-02, VOL-II-9.2-01, VOL-II-9.3-01, VOL-II-9.4-01, VOL-II-9.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-II-T2-6-1, VOL-II-T2-6-2, VOL-II-T2-6-3, VOL-II-T2-6-4, VOL-II-T2-6-5, VOL-II-T2-6-6; duration 20 WD is an ASSUMPTION: technical_proposal)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -38464,7 +38829,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
+          <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-6.2-01; ADD-03-T22n3-01; VOL-I-11.3-01; VOL-I-9.2-01; VOL-I-9.7-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -38472,17 +38837,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>I-A5-poa-legalise</t>
+          <t>I-A5-fin-model-build</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>A5 poa-legalise: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-17 (after poa) is after the latest start 2026-11-10; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 10 WD is an ASSUMPTION: poa_legalisation)</t>
+          <t>A5 fin-model-build: INFEASIBLE by 3 WD (total float -3 WD: latest start 2026-10-29 is before the planning date 2026-11-03; not compressed) (ADD-03-Q20-01, VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 15 WD is an ASSUMPTION: fin_model_build)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -38492,7 +38857,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-Q16-01; VOL-I-9.1h-01; VOL-I-9.3-01</t>
+          <t>ADD-03-Q20-01; VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -38500,17 +38865,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-model-freeze</t>
+          <t>I-A5-poa</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-model-freeze: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-24 (after fin-model-build) is after the latest start 2026-11-19; not compressed) (ADD-03-Q20-01, VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 1 WD is an ASSUMPTION: fin_model_freeze)</t>
+          <t>A5 poa: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-10 (after poa-resolutions) is after the latest start 2026-11-03; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 5 WD is an ASSUMPTION: poa_notarisation)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -38520,7 +38885,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-Q20-01; VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
+          <t>ADD-03-Q16-01; VOL-I-9.1h-01; VOL-I-9.3-01</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -38528,17 +38893,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-assumptions</t>
+          <t>I-A5-pcg-execution</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-assumptions: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-25 (after fin-model-freeze) is after the latest start 2026-11-22; not compressed) (VOL-I-10.6-01; duration 2 WD is an ASSUMPTION: fin_assumptions_schedule)</t>
+          <t>A5 pcg-execution: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-17 (after pcg-wording) is after the latest start 2026-11-10; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_execution)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -38548,7 +38913,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.6-01</t>
+          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -38556,17 +38921,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>I-A5-form-4f</t>
+          <t>I-A5-poa-legalise</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>A5 form-4f: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-25 (after fin-model-freeze) is after the latest start 2026-11-22; not compressed) (VOL-I-10.1-01, VOL-I-10.2-01, VOL-I-10.4-01, VOL-I-10.5-01, VOL-IV-F4F-01, VOL-IV-F4F-02; duration 2 WD is an ASSUMPTION: form_4f_preparation)</t>
+          <t>A5 poa-legalise: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-17 (after poa) is after the latest start 2026-11-10; not compressed) (ADD-03-Q16-01, VOL-I-9.1h-01, VOL-I-9.3-01; duration 10 WD is an ASSUMPTION: poa_legalisation)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -38576,7 +38941,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.4-01; VOL-I-10.5-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
+          <t>ADD-03-Q16-01; VOL-I-9.1h-01; VOL-I-9.3-01</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -38584,17 +38949,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-fin-model-freeze</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-22 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 fin-model-freeze: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-24 (after fin-model-build) is after the latest start 2026-11-19; not compressed) (ADD-03-Q20-01, VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 1 WD is an ASSUMPTION: fin_model_freeze)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -38604,7 +38969,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-6.8-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>ADD-03-Q20-01; VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -38612,17 +38977,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-b</t>
+          <t>I-A5-fin-assumptions</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-b: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-29 (after form-4f) is after the latest start 2026-11-24; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 fin-assumptions: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-25 (after fin-model-freeze) is after the latest start 2026-11-22; not compressed) (VOL-I-10.6-01; duration 2 WD is an ASSUMPTION: fin_assumptions_schedule)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -38632,7 +38997,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-6.8-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-10.6-01</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -38640,17 +39005,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-form-4f</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-23 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (ADD-03-6.8-01, ADD-03-Q20-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 form-4f: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-25 (after fin-model-freeze) is after the latest start 2026-11-22; not compressed) (VOL-I-10.1-01, VOL-I-10.2-01, VOL-I-10.4-01, VOL-I-10.5-01, VOL-IV-F4F-01, VOL-IV-F4F-02; duration 2 WD is an ASSUMPTION: form_4f_preparation)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -38660,7 +39025,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-6.8-01; ADD-03-Q20-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.4-01; VOL-I-10.5-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -38668,12 +39033,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-23 (after copies) is after the latest start 2026-11-25; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-22 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -38696,12 +39061,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-assemble-envelope-b</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-24 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 assemble-envelope-b: INFEASIBLE by 3 WD (total float -3 WD: earliest start 2026-11-29 (after form-4f) is after the latest start 2026-11-24; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -38724,17 +39089,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-audit-opinion</t>
+          <t>I-A5-copies</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-opinion: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
+          <t>A5 copies: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-23 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (ADD-03-6.8-01, ADD-03-Q20-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -38744,7 +39109,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01</t>
+          <t>ADD-03-6.8-01; ADD-03-Q20-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -38752,17 +39117,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-audit-review</t>
+          <t>I-A5-seal-and-mark</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-review: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
+          <t>A5 seal-and-mark: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-23 (after copies) is after the latest start 2026-11-25; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -38772,7 +39137,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01</t>
+          <t>ADD-03-6.8-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -38780,17 +39145,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-auditor-appoint</t>
+          <t>I-A5-deliver</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>A5 model-auditor-appoint: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
+          <t>A5 deliver: INFEASIBLE by 20 WD (total float -20 WD: earliest start 2026-12-24 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (ADD-03-6.8-01, ADD-03-Q20-02, VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -38800,7 +39165,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-12.5-01</t>
+          <t>ADD-03-6.8-01; ADD-03-Q20-02; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -38808,33 +39173,117 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
+          <t>I-A5-model-audit-opinion</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>A5 model-audit-opinion: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03-12.5-01</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-model-audit-review</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>A5 model-audit-review: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03-12.5-01</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-model-auditor-appoint</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>A5 model-auditor-appoint: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-12.5-01; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03-12.5-01</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 20 WD; lcc-certificate INFEASIBLE by 20 WD; pcg-wording INFEASIBLE by 5 WD; poa-resolutions INFEASIBLE by 5 WD; technical-proposal INFEASIBLE by 5 WD; fin-model-build INFEASIBLE by 3 WD; poa INFEASIBLE by 5 WD; pcg-execution INFEASIBLE by 5 WD; poa-legalise INFEASIBLE by 5 WD; fin-model-freeze INFEASIBLE by 3 WD; fin-assumptions INFEASIBLE by 3 WD; form-4f INFEASIBLE by 3 WD; assemble-envelope-a INFEASIBLE by 20 WD; assemble-envelope-b INFEASIBLE by 3 WD; copies INFEASIBLE by 20 WD; seal-and-mark INFEASIBLE by 20 WD; deliver INFEASIBLE by 20 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-6.2-01; ADD-03-6.8-01; ADD-03-Q16-01; ADD-03-Q20-01; ADD-03-Q20-02; ADD-03-T22n3-01; VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.3-01; VOL-I-10.4-01; VOL-I-10.5-01; VOL-I-10.6-01; VOL-I-11.3-01; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-8.7-01; VOL-I-9.1-01; VOL-I-9.1h-01; VOL-I-9.2-01; VOL-I-9.3-01; VOL-I-9.7-01; VOL-I-App3-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41993,4 +42442,1487 @@
   <autoFilter ref="A1:E52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Issues</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FIN-STANDING</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FORM-4C</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-MULTIPLE-PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-DEBARMENT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-INVESTMENT-LICENCE</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.9-01</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-PROCESS-DESIGN</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-3.1-01</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RELIABILITY-RUN</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.2-01</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-UNAVAILABILITY</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-02</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RAMP-UP-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.3-01</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-MECHANISM</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-QUOTED-PRICE</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.2-01</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-01</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCIAL-MODEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>REL-MODEL-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-02</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>possible impact</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.6-01</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-39.1-01</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V:39.3</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 7 (deductions)</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>the Environmental Permit issued for the site</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>I-PERMIT</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>